--- a/課題.xlsx
+++ b/課題.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\Drone3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53866474-FB64-4606-9E18-92B44E0BF3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{752F55A4-6D63-4D4C-92FD-1B114DC592E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="1060" windowWidth="17770" windowHeight="10020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1430" yWindow="1980" windowWidth="17770" windowHeight="10020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -88,16 +89,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>一定速度以上で衝突時にスピードを0に</t>
-    <rPh sb="0" eb="6">
-      <t>イッテイソクドイジョウ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ショウトツジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>水面を泳ぐ挙動とかに使えそう</t>
     <rPh sb="0" eb="2">
       <t>スイメン</t>
@@ -133,6 +124,30 @@
     </rPh>
     <rPh sb="38" eb="40">
       <t>ウワガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cameraクラスの</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一定速度以上で衝突時にスピードを0に
+そもそも壁に接触しないゲームにすれば解決</t>
+    <rPh sb="0" eb="6">
+      <t>イッテイソクドイジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ショウトツジ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カイケツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -177,14 +192,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -485,87 +507,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="2" width="8.6640625" style="1"/>
+    <col min="3" max="3" width="28.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
+    <row r="2" spans="1:6" ht="54">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="b">
+      <c r="B2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="b">
+      <c r="B3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="b">
+      <c r="B4" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="b">
+      <c r="B5" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="b">
+      <c r="B6" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="b">
+      <c r="B7" s="2" t="b">
         <v>0</v>
       </c>
     </row>

--- a/課題.xlsx
+++ b/課題.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\Drone3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{752F55A4-6D63-4D4C-92FD-1B114DC592E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320505F3-3795-469B-8B25-8C0FC994A28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1430" yWindow="1980" windowWidth="17770" windowHeight="10020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -125,10 +124,6 @@
     <rPh sb="38" eb="40">
       <t>ウワガ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cameraクラスの</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -148,6 +143,59 @@
     </rPh>
     <rPh sb="37" eb="39">
       <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cameraクラスの独立</t>
+    <rPh sb="10" eb="12">
+      <t>ドクリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾が壁に当たった途端強制終了</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トタン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョウセイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブレークポイントだった</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>阿呆の極み</t>
+    <rPh sb="0" eb="2">
+      <t>アホウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3Dオブジェクトが一切描画されない</t>
+    <rPh sb="9" eb="11">
+      <t>イッサイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ビョウガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -509,7 +557,7 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="1"/>
-    <col min="3" max="3" width="28.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="59.25" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.08203125" style="1" bestFit="1" customWidth="1"/>
@@ -547,7 +595,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>7</v>
@@ -558,7 +606,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
@@ -567,7 +615,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -575,7 +623,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -584,6 +641,9 @@
       </c>
       <c r="B5" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6">
